--- a/IPO-Examenes.xlsx
+++ b/IPO-Examenes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Artur\Documents\Universidad\3º-cuatri2\ProgramaTest\programa-estudio-calidad-software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D37F043-CD85-402C-9537-8220C981168E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0253DE-B18D-4C00-B7DF-B915CEC42565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="15576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="282">
   <si>
     <t>Tema</t>
   </si>
@@ -523,9 +523,6 @@
     <t>¿Qué opción es la que mejor define la robustez en usabilidad?</t>
   </si>
   <si>
-    <t>REVISAR: la opción marcada define flexibilidad, no robustez.</t>
-  </si>
-  <si>
     <t>¿Qué opción no es un principio de flexibilidad?</t>
   </si>
   <si>
@@ -551,9 +548,6 @@
   </si>
   <si>
     <t>Capacidad de sustitución</t>
-  </si>
-  <si>
-    <t>REVISAR con apuntes: posible inconsistencia en opciones/respuesta.</t>
   </si>
   <si>
     <t>¿Qué son y cuándo se aplican las guías abstractas de diseño?</t>
@@ -1004,7 +998,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PreguntasUnicasTable" displayName="PreguntasUnicasTable" ref="A1:K59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PreguntasUnicasTable" displayName="PreguntasUnicasTable" ref="A1:K57">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Tema"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Pregunta"/>
@@ -1202,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2031,9 +2025,7 @@
       <c r="G25" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>118</v>
-      </c>
+      <c r="H25" s="3"/>
       <c r="I25" s="3">
         <v>3</v>
       </c>
@@ -2471,71 +2463,69 @@
       </c>
       <c r="K38" s="3"/>
     </row>
-    <row r="39" spans="1:11" ht="41.4">
+    <row r="39" spans="1:11">
       <c r="A39" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="I39" s="3">
         <v>1</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>166</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="K39" s="3"/>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I40" s="3">
         <v>1</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K40" s="3"/>
     </row>
@@ -2544,13 +2534,13 @@
         <v>88</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>173</v>
@@ -2559,309 +2549,307 @@
         <v>174</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I41" s="3">
         <v>1</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="K41" s="3"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" ht="41.4">
       <c r="A42" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>170</v>
+        <v>13</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>173</v>
+        <v>16</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>174</v>
+        <v>14</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>175</v>
+        <v>13</v>
       </c>
       <c r="I42" s="3">
         <v>1</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="K42" s="3"/>
     </row>
-    <row r="43" spans="1:11" ht="41.4">
+    <row r="43" spans="1:11" ht="55.2">
       <c r="A43" s="3" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I43" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>176</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="K43" s="3"/>
     </row>
     <row r="44" spans="1:11" ht="41.4">
       <c r="A44" s="3" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>13</v>
+        <v>183</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
       <c r="I44" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="K44" s="3"/>
     </row>
-    <row r="45" spans="1:11" ht="55.2">
+    <row r="45" spans="1:11" ht="41.4">
       <c r="A45" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K45" s="3"/>
+    </row>
+    <row r="46" spans="1:11" ht="27.6">
+      <c r="A46" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K46" s="3"/>
+    </row>
+    <row r="47" spans="1:11" ht="27.6">
+      <c r="A47" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="1:11" ht="41.4">
-      <c r="A46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="D47" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D46" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="I46" s="3">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="1:11" ht="41.4">
-      <c r="A47" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="I47" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="K47" s="3"/>
     </row>
     <row r="48" spans="1:11" ht="27.6">
       <c r="A48" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="K48" s="3"/>
     </row>
     <row r="49" spans="1:11" ht="27.6">
       <c r="A49" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>188</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="K49" s="3"/>
     </row>
     <row r="50" spans="1:11" ht="27.6">
       <c r="A50" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="I50" s="3">
         <v>1</v>
@@ -2873,305 +2861,239 @@
     </row>
     <row r="51" spans="1:11" ht="27.6">
       <c r="A51" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I51" s="3">
         <v>1</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="K51" s="3"/>
     </row>
-    <row r="52" spans="1:11" ht="27.6">
+    <row r="52" spans="1:11" ht="69">
       <c r="A52" s="3" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="I52" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="K52" s="3"/>
     </row>
-    <row r="53" spans="1:11" ht="27.6">
+    <row r="53" spans="1:11" ht="41.4">
       <c r="A53" s="3" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="I53" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="K53" s="3"/>
     </row>
-    <row r="54" spans="1:11" ht="69">
+    <row r="54" spans="1:11" ht="27.6">
       <c r="A54" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>215</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I54" s="3">
+        <v>2</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K54" s="3"/>
+    </row>
+    <row r="55" spans="1:11" ht="27.6">
+      <c r="A55" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I55" s="3">
+        <v>2</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K55" s="3"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G56" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="1:11" ht="41.4">
-      <c r="A55" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I55" s="3">
-        <v>3</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="1:11" ht="27.6">
-      <c r="A56" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="H56" s="3" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="I56" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="K56" s="3"/>
     </row>
     <row r="57" spans="1:11" ht="27.6">
       <c r="A57" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>225</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I57" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="A58" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="1:11" ht="27.6">
-      <c r="A59" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E59" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K57" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>239</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K59">
+  <conditionalFormatting sqref="K2:K57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEN($K2)&gt;0</formula>
     </cfRule>
@@ -3253,10 +3175,10 @@
     </row>
     <row r="5" spans="1:4" ht="69">
       <c r="A5" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C5" s="1">
         <v>5</v>
@@ -3281,10 +3203,10 @@
     </row>
     <row r="7" spans="1:4" ht="55.2">
       <c r="A7" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
@@ -3337,10 +3259,10 @@
     </row>
     <row r="11" spans="1:4" ht="41.4">
       <c r="A11" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -3351,30 +3273,30 @@
     </row>
     <row r="12" spans="1:4" ht="41.4">
       <c r="A12" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="41.4">
       <c r="A13" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="27.6">
@@ -3575,10 +3497,10 @@
     </row>
     <row r="28" spans="1:4" ht="27.6">
       <c r="A28" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
@@ -3589,10 +3511,10 @@
     </row>
     <row r="29" spans="1:4" ht="27.6">
       <c r="A29" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C29" s="1">
         <v>2</v>
@@ -3603,10 +3525,10 @@
     </row>
     <row r="30" spans="1:4" ht="27.6">
       <c r="A30" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
@@ -3617,16 +3539,16 @@
     </row>
     <row r="31" spans="1:4" ht="27.6">
       <c r="A31" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C31" s="1">
         <v>2</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -3647,13 +3569,13 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.4">
       <c r="A1" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B2" s="1">
         <v>6</v>
@@ -3661,7 +3583,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B3" s="1">
         <v>113</v>
@@ -3669,7 +3591,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B4" s="1">
         <v>59</v>
@@ -3677,7 +3599,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B5" s="1">
         <v>30</v>
@@ -3685,7 +3607,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B6" s="1">
         <v>54</v>
@@ -3697,10 +3619,10 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3713,7 +3635,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
@@ -3737,7 +3659,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B13" s="1">
         <v>6</v>
@@ -3765,10 +3687,10 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3809,10 +3731,10 @@
     </row>
     <row r="23" spans="1:2" ht="41.4">
       <c r="A23" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3948,13 +3870,13 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
@@ -3986,10 +3908,10 @@
         <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>88</v>
@@ -4021,10 +3943,10 @@
         <v>60</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
@@ -4056,34 +3978,34 @@
         <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="27.6">
@@ -4091,34 +4013,34 @@
         <v>60</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="27.6">
@@ -4126,10 +4048,10 @@
         <v>60</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>88</v>
@@ -4161,10 +4083,10 @@
         <v>60</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>88</v>
@@ -4196,10 +4118,10 @@
         <v>60</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>88</v>
@@ -4231,10 +4153,10 @@
         <v>60</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>63</v>
@@ -4266,10 +4188,10 @@
         <v>60</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>18</v>
@@ -4301,10 +4223,10 @@
         <v>60</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>88</v>
@@ -4336,10 +4258,10 @@
         <v>60</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>63</v>
@@ -4371,34 +4293,34 @@
         <v>60</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="J13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="27.6">
@@ -4406,34 +4328,34 @@
         <v>60</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="27.6">
@@ -4441,10 +4363,10 @@
         <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>88</v>
@@ -4476,10 +4398,10 @@
         <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>88</v>
@@ -4511,10 +4433,10 @@
         <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>88</v>
@@ -4546,34 +4468,34 @@
         <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="41.4">
@@ -4581,10 +4503,10 @@
         <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>88</v>
@@ -4616,34 +4538,34 @@
         <v>60</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="27.6">
@@ -4651,34 +4573,34 @@
         <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="27.6">
@@ -4686,34 +4608,34 @@
         <v>40</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="J22" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="27.6">
@@ -4721,34 +4643,34 @@
         <v>40</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="J23" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="27.6">
@@ -4756,10 +4678,10 @@
         <v>40</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>88</v>
@@ -4791,10 +4713,10 @@
         <v>40</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>18</v>
@@ -4826,34 +4748,34 @@
         <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="27.6">
@@ -4861,34 +4783,34 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="27.6">
@@ -4896,10 +4818,10 @@
         <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>88</v>
@@ -4931,34 +4853,34 @@
         <v>40</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="27.6">
@@ -4966,10 +4888,10 @@
         <v>40</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>88</v>
@@ -5001,10 +4923,10 @@
         <v>40</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>88</v>
@@ -5036,10 +4958,10 @@
         <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>63</v>
@@ -5071,10 +4993,10 @@
         <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>88</v>
@@ -5106,10 +5028,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>18</v>
@@ -5141,10 +5063,10 @@
         <v>40</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>88</v>
@@ -5176,10 +5098,10 @@
         <v>40</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>88</v>
@@ -5211,10 +5133,10 @@
         <v>46</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>88</v>
@@ -5246,34 +5168,34 @@
         <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="41.4">
@@ -5281,10 +5203,10 @@
         <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>88</v>
@@ -5316,34 +5238,34 @@
         <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="27.6">
@@ -5351,10 +5273,10 @@
         <v>46</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>88</v>
@@ -5386,10 +5308,10 @@
         <v>46</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>63</v>
@@ -5421,34 +5343,34 @@
         <v>46</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="27.6">
@@ -5456,10 +5378,10 @@
         <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>18</v>
@@ -5491,34 +5413,34 @@
         <v>46</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="I45" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="41.4">
@@ -5526,10 +5448,10 @@
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>88</v>
@@ -5561,34 +5483,34 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H47" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="J47" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="27.6">
@@ -5596,34 +5518,34 @@
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G48" s="1" t="s">
+      <c r="J48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="27.6">
@@ -5631,10 +5553,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>88</v>
@@ -5666,10 +5588,10 @@
         <v>46</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>63</v>
@@ -5701,10 +5623,10 @@
         <v>46</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>88</v>
@@ -5716,10 +5638,10 @@
         <v>98</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>96</v>
@@ -5736,10 +5658,10 @@
         <v>46</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>47</v>
@@ -5771,34 +5693,34 @@
         <v>46</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="H53" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="55.2">
@@ -5806,10 +5728,10 @@
         <v>46</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>88</v>
@@ -5841,10 +5763,10 @@
         <v>46</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>88</v>
@@ -5876,10 +5798,10 @@
         <v>46</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>88</v>
@@ -5911,10 +5833,10 @@
         <v>62</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>88</v>
@@ -5946,10 +5868,10 @@
         <v>62</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>88</v>
@@ -5981,10 +5903,10 @@
         <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>88</v>
@@ -6002,7 +5924,7 @@
         <v>97</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>3</v>
@@ -6016,34 +5938,34 @@
         <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E60" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="G60" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="27.6">
@@ -6051,34 +5973,34 @@
         <v>62</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="H61" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="55.2">
@@ -6086,10 +6008,10 @@
         <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>47</v>
@@ -6121,10 +6043,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>47</v>
@@ -6156,10 +6078,10 @@
         <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>88</v>
@@ -6191,10 +6113,10 @@
         <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>18</v>
@@ -6226,34 +6148,34 @@
         <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G66" s="1" t="s">
+      <c r="I66" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="27.6">
@@ -6261,10 +6183,10 @@
         <v>62</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>88</v>
@@ -6296,16 +6218,16 @@
         <v>62</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>13</v>
@@ -6331,10 +6253,10 @@
         <v>62</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>63</v>
@@ -6366,34 +6288,34 @@
         <v>62</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D70" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="G70" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="41.4">
@@ -6401,34 +6323,34 @@
         <v>62</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D71" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="I71" s="1" t="s">
+      <c r="J71" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="41.4">
@@ -6436,10 +6358,10 @@
         <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>88</v>
@@ -6471,10 +6393,10 @@
         <v>62</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>88</v>
@@ -6506,10 +6428,10 @@
         <v>62</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>88</v>
@@ -6541,10 +6463,10 @@
         <v>62</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>63</v>
@@ -6576,34 +6498,34 @@
         <v>62</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E76" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="J76" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="27.6">
@@ -6611,10 +6533,10 @@
         <v>17</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>18</v>
@@ -6646,10 +6568,10 @@
         <v>17</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>88</v>
@@ -6681,34 +6603,34 @@
         <v>17</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H79" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="41.4">
@@ -6716,34 +6638,34 @@
         <v>17</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H80" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F80" s="1" t="s">
+      <c r="I80" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="27.6">
@@ -6751,34 +6673,34 @@
         <v>17</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I81" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="27.6">
@@ -6786,34 +6708,34 @@
         <v>17</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E82" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G82" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="I82" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="27.6">
@@ -6821,34 +6743,34 @@
         <v>17</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H83" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I83" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="55.2">
@@ -6856,10 +6778,10 @@
         <v>17</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>63</v>
@@ -6891,10 +6813,10 @@
         <v>17</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>63</v>
@@ -6926,10 +6848,10 @@
         <v>17</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>47</v>
@@ -6961,34 +6883,34 @@
         <v>17</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E87" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="G87" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H87" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="I87" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="27.6">
@@ -6996,10 +6918,10 @@
         <v>17</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>88</v>
@@ -7031,10 +6953,10 @@
         <v>17</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>88</v>
@@ -7066,10 +6988,10 @@
         <v>17</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>88</v>
@@ -7101,10 +7023,10 @@
         <v>17</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>88</v>
@@ -7136,34 +7058,34 @@
         <v>17</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E92" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I92" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="41.4">
@@ -7171,10 +7093,10 @@
         <v>17</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>11</v>
@@ -7206,10 +7128,10 @@
         <v>17</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>88</v>
@@ -7241,10 +7163,10 @@
         <v>17</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>18</v>
@@ -7276,10 +7198,10 @@
         <v>17</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>88</v>
@@ -7311,10 +7233,10 @@
         <v>84</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>63</v>
@@ -7346,10 +7268,10 @@
         <v>84</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>18</v>
@@ -7381,10 +7303,10 @@
         <v>84</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>88</v>
@@ -7416,34 +7338,34 @@
         <v>84</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="I100" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="27.6">
@@ -7451,10 +7373,10 @@
         <v>84</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>88</v>
@@ -7486,10 +7408,10 @@
         <v>84</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>88</v>
@@ -7521,10 +7443,10 @@
         <v>84</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>88</v>
@@ -7556,10 +7478,10 @@
         <v>84</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>88</v>
@@ -7591,34 +7513,34 @@
         <v>84</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H105" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F105" s="1" t="s">
+      <c r="I105" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="41.4">
@@ -7626,10 +7548,10 @@
         <v>84</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>88</v>
@@ -7661,10 +7583,10 @@
         <v>84</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>63</v>
@@ -7696,10 +7618,10 @@
         <v>84</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>88</v>
@@ -7731,10 +7653,10 @@
         <v>84</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>88</v>
@@ -7766,10 +7688,10 @@
         <v>84</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>63</v>
@@ -7801,10 +7723,10 @@
         <v>84</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>88</v>
@@ -7836,34 +7758,34 @@
         <v>84</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G112" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H112" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="H112" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="I112" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="41.4">
@@ -7871,10 +7793,10 @@
         <v>84</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>47</v>
@@ -7892,7 +7814,7 @@
         <v>57</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J113" s="1" t="s">
         <v>2</v>
@@ -7906,25 +7828,25 @@
         <v>84</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>121</v>
@@ -7933,7 +7855,7 @@
         <v>2</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/IPO-Examenes.xlsx
+++ b/IPO-Examenes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Artur\Documents\Universidad\3º-cuatri2\ProgramaTest\programa-estudio-calidad-software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0253DE-B18D-4C00-B7DF-B915CEC42565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACEEBEF-D5D9-49BD-B77E-90C3FBA6D2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="15576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3080,7 +3080,7 @@
         <v>2</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I57" s="3">
         <v>1</v>
